--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.168.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.168.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.168.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.168.xlsx
@@ -416,28 +416,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="59" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.168.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.168.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0168.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0168.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -600,21 +600,25 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 7Q (letter/digit mix) :: 69â€”7Q</t>
+          <t>L126: suspicious token(s): 7Q (letter/digit mix) :: 69—7Q</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 46 â€” 47</t>
+          <t>L25: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 46â€”47</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]161</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]161</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 23</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L33: isolated marker/symbol line :: 12</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]161</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -636,7 +640,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L150: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 38</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -657,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -672,12 +680,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 15 â€” 116</t>
+          <t>L82: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 70â€”71</t>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -689,7 +697,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: 23</t>
+          <t>L33: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -739,12 +747,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 11 â€” 112</t>
+          <t>L89: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 15â€”116</t>
+          <t>L128: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -756,7 +764,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: 20</t>
+          <t>L35: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -782,12 +790,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -802,24 +810,24 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: For Subp Ã¦ na ad audiendum</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 86â€”87â€”122</t>
+          <t>L142: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L8: symbol-only separator/garbage line :: 70-71</t>
+          <t>L6: symbol-only separator/garbage line :: 46 — 47</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L45: symbol-only separator/garbage line :: 113 -</t>
+          <t>L37: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -861,24 +869,24 @@
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L92: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L146: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L9: isolated marker/symbol line :: 113</t>
+          <t>L8: symbol-only separator/garbage line :: 70-71</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L51: symbol-only separator/garbage line :: . 107</t>
+          <t>L40: symbol-only separator/garbage line :: 46—47</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -921,25 +929,25 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 7Q (letter/digit mix) :: 69â€”7Q</t>
+          <t>L150: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 38</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L12: isolated marker/symbol line :: 161</t>
+          <t>L9: isolated marker/symbol line :: 113</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L57: symbol-only separator/garbage line :: , . 116</t>
+          <t>L43: symbol-only separator/garbage line :: 70—71</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L116: punctuation artifact: repeated periods :: (See Â« Additions," &amp;c.. No. 5).</t>
+          <t>L116: punctuation artifact: repeated periods :: (See « Additions," &amp;c.. No. 5).</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
@@ -976,19 +984,19 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L128: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L158: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L16: isolated marker/symbol line :: 68</t>
+          <t>L10: symbol-only separator/garbage line :: 15 — 116</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L59: isolated marker/symbol line :: 23</t>
+          <t>L45: symbol-only separator/garbage line :: 113 -</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1025,21 +1033,17 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: -71â€”72</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L17: isolated marker/symbol line :: .</t>
+          <t>L12: isolated marker/symbol line :: 161</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: 91</t>
+          <t>L47: symbol-only separator/garbage line :: 15—116</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1066,7 +1070,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1076,21 +1080,17 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 11â€”112</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L18: isolated marker/symbol line :: 12</t>
+          <t>L16: isolated marker/symbol line :: 68</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L64: symbol-only separator/garbage line :: .90</t>
+          <t>L51: symbol-only separator/garbage line :: . 107</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1127,21 +1127,17 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L21: symbol-only separator/garbage line :: . 107</t>
+          <t>L17: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: 92</t>
+          <t>L57: symbol-only separator/garbage line :: , . 116</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1163,12 +1159,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1178,21 +1174,17 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L23: isolated marker/symbol line :: 107</t>
+          <t>L18: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L68: symbol-only separator/garbage line :: . 109</t>
+          <t>L59: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1229,21 +1221,17 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L150: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 38</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: 116</t>
+          <t>L21: symbol-only separator/garbage line :: . 107</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: 112</t>
+          <t>L60: symbol-only separator/garbage line :: . 86—87—122</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1270,7 +1258,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1280,21 +1268,17 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: 23</t>
+          <t>L23: isolated marker/symbol line :: 107</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L72: symbol-only separator/garbage line :: . 115</t>
+          <t>L62: isolated marker/symbol line :: 91</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1331,21 +1315,17 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L166: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 7â€”10</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L36: symbol-only separator/garbage line :: 69-70</t>
+          <t>L25: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 141</t>
+          <t>L64: symbol-only separator/garbage line :: .90</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1382,21 +1362,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 88â€”89</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L37: symbol-only separator/garbage line :: - 71-72</t>
+          <t>L29: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: ?</t>
+          <t>L66: isolated marker/symbol line :: 92</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1433,21 +1409,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L184: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 58â€”59</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L38: symbol-only separator/garbage line :: . 108</t>
+          <t>L32: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L68: symbol-only separator/garbage line :: . 109</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1477,12 +1449,12 @@
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 109</t>
+          <t>L36: symbol-only separator/garbage line :: 69-70</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L128: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L70: isolated marker/symbol line :: 112</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1512,12 +1484,12 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: 116</t>
+          <t>L37: symbol-only separator/garbage line :: - 71-72</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L132: symbol-only separator/garbage line :: .108</t>
+          <t>L72: symbol-only separator/garbage line :: . 115</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1547,12 +1519,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L43: symbol-only separator/garbage line :: . 86-87-122</t>
+          <t>L38: symbol-only separator/garbage line :: . 108</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L134: isolated marker/symbol line :: 109</t>
+          <t>L74: isolated marker/symbol line :: 141</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1582,12 +1554,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L45: isolated marker/symbol line :: 91</t>
+          <t>L39: isolated marker/symbol line :: 109</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L138: isolated marker/symbol line :: 116</t>
+          <t>L76: isolated marker/symbol line :: ?</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1617,12 +1589,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: 90</t>
+          <t>L40: symbol-only separator/garbage line :: 11 — 112</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: %</t>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1652,12 +1624,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 92</t>
+          <t>L41: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L128: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1687,12 +1659,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 109</t>
+          <t>L43: symbol-only separator/garbage line :: . 86-87-122</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L130: symbol-only separator/garbage line :: -71—72</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1722,12 +1694,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 112</t>
+          <t>L45: isolated marker/symbol line :: 91</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L148: isolated marker/symbol line :: 38</t>
+          <t>L132: symbol-only separator/garbage line :: .108</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1757,12 +1729,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: 115</t>
+          <t>L47: isolated marker/symbol line :: 90</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L152: isolated marker/symbol line :: 39</t>
+          <t>L134: isolated marker/symbol line :: 109</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1792,12 +1764,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: 141</t>
+          <t>L49: isolated marker/symbol line :: 92</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L156: isolated marker/symbol line :: 39</t>
+          <t>L136: symbol-only separator/garbage line :: 11—112</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1827,12 +1799,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: 38</t>
+          <t>L51: isolated marker/symbol line :: 109</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L138: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1862,12 +1834,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L64: isolated marker/symbol line :: 2</t>
+          <t>L53: isolated marker/symbol line :: 112</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L160: isolated marker/symbol line :: .2</t>
+          <t>L140: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1897,12 +1869,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L67: symbol-only separator/garbage line :: 7-10</t>
+          <t>L55: isolated marker/symbol line :: 115</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L168: isolated marker/symbol line :: 7</t>
+          <t>L142: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1932,12 +1904,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L68: isolated marker/symbol line :: 7</t>
+          <t>L57: isolated marker/symbol line :: 141</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L170: symbol-only separator/garbage line :: .10</t>
+          <t>L146: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1967,12 +1939,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L69: symbol-only separator/garbage line :: . 10</t>
+          <t>L63: isolated marker/symbol line :: 38</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L174: symbol-only separator/garbage line :: .12</t>
+          <t>L148: isolated marker/symbol line :: 38</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2002,12 +1974,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 12</t>
+          <t>L64: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L176: isolated marker/symbol line :: %</t>
+          <t>L150: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 38</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2037,12 +2009,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: 10</t>
+          <t>L67: symbol-only separator/garbage line :: 7-10</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L182: symbol-only separator/garbage line :: . 58</t>
+          <t>L152: isolated marker/symbol line :: 39</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2072,12 +2044,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 7</t>
+          <t>L68: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L186: isolated marker/symbol line :: 57</t>
+          <t>L156: isolated marker/symbol line :: 39</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2107,12 +2079,12 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: 38</t>
+          <t>L69: symbol-only separator/garbage line :: . 10</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L188: isolated marker/symbol line :: 10</t>
+          <t>L158: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2142,12 +2114,12 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 39</t>
+          <t>L71: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L189: isolated marker/symbol line :: .7</t>
+          <t>L160: isolated marker/symbol line :: .2</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2177,10 +2149,14 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: .</t>
-        </is>
-      </c>
-      <c r="O38" s="1" t="inlineStr"/>
+          <t>L72: isolated marker/symbol line :: 10</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>L166: symbol-only separator/garbage line :: 7—10</t>
+        </is>
+      </c>
       <c r="P38" s="1" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr"/>
       <c r="R38" s="1" t="inlineStr"/>
@@ -2208,10 +2184,14 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: :</t>
-        </is>
-      </c>
-      <c r="O39" s="1" t="inlineStr"/>
+          <t>L73: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>L168: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr"/>
       <c r="R39" s="1" t="inlineStr"/>
@@ -2239,10 +2219,14 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: 39</t>
-        </is>
-      </c>
-      <c r="O40" s="1" t="inlineStr"/>
+          <t>L75: isolated marker/symbol line :: 38</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>L170: symbol-only separator/garbage line :: .10</t>
+        </is>
+      </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr"/>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2270,10 +2254,14 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L86: symbol-only separator/garbage line :: 88-89</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr"/>
+          <t>L77: isolated marker/symbol line :: 39</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>L174: symbol-only separator/garbage line :: .12</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2301,10 +2289,14 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="inlineStr"/>
+          <t>L80: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>L176: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2332,10 +2324,14 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: æ°”</t>
-        </is>
-      </c>
-      <c r="O43" s="1" t="inlineStr"/>
+          <t>L81: isolated marker/symbol line :: :</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>L178: symbol-only separator/garbage line :: . 88—89</t>
+        </is>
+      </c>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
       <c r="R43" s="1" t="inlineStr"/>
@@ -2363,10 +2359,14 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 58</t>
-        </is>
-      </c>
-      <c r="O44" s="1" t="inlineStr"/>
+          <t>L82: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>L182: symbol-only separator/garbage line :: . 58</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2394,10 +2394,14 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L97: symbol-only separator/garbage line :: 58-59</t>
-        </is>
-      </c>
-      <c r="O45" s="1" t="inlineStr"/>
+          <t>L83: isolated marker/symbol line :: 39</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="inlineStr">
+        <is>
+          <t>L184: symbol-only separator/garbage line :: . 58—59</t>
+        </is>
+      </c>
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr"/>
       <c r="R45" s="1" t="inlineStr"/>
@@ -2425,10 +2429,14 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: 57</t>
-        </is>
-      </c>
-      <c r="O46" s="1" t="inlineStr"/>
+          <t>L86: symbol-only separator/garbage line :: 88-89</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>L186: isolated marker/symbol line :: 57</t>
+        </is>
+      </c>
       <c r="P46" s="1" t="inlineStr"/>
       <c r="Q46" s="1" t="inlineStr"/>
       <c r="R46" s="1" t="inlineStr"/>
@@ -2440,6 +2448,200 @@
       <c r="X46" s="1" t="inlineStr"/>
       <c r="Y46" s="1" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr"/>
+      <c r="B47" s="1" t="inlineStr"/>
+      <c r="C47" s="1" t="inlineStr"/>
+      <c r="D47" s="1" t="inlineStr"/>
+      <c r="E47" s="1" t="inlineStr"/>
+      <c r="F47" s="1" t="inlineStr"/>
+      <c r="G47" s="1" t="inlineStr"/>
+      <c r="H47" s="1" t="inlineStr"/>
+      <c r="I47" s="1" t="inlineStr"/>
+      <c r="J47" s="1" t="inlineStr"/>
+      <c r="K47" s="1" t="inlineStr"/>
+      <c r="L47" s="1" t="inlineStr"/>
+      <c r="M47" s="1" t="inlineStr"/>
+      <c r="N47" s="1" t="inlineStr">
+        <is>
+          <t>L89: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>L188: isolated marker/symbol line :: 10</t>
+        </is>
+      </c>
+      <c r="P47" s="1" t="inlineStr"/>
+      <c r="Q47" s="1" t="inlineStr"/>
+      <c r="R47" s="1" t="inlineStr"/>
+      <c r="S47" s="1" t="inlineStr"/>
+      <c r="T47" s="1" t="inlineStr"/>
+      <c r="U47" s="1" t="inlineStr"/>
+      <c r="V47" s="1" t="inlineStr"/>
+      <c r="W47" s="1" t="inlineStr"/>
+      <c r="X47" s="1" t="inlineStr"/>
+      <c r="Y47" s="1" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr"/>
+      <c r="B48" s="1" t="inlineStr"/>
+      <c r="C48" s="1" t="inlineStr"/>
+      <c r="D48" s="1" t="inlineStr"/>
+      <c r="E48" s="1" t="inlineStr"/>
+      <c r="F48" s="1" t="inlineStr"/>
+      <c r="G48" s="1" t="inlineStr"/>
+      <c r="H48" s="1" t="inlineStr"/>
+      <c r="I48" s="1" t="inlineStr"/>
+      <c r="J48" s="1" t="inlineStr"/>
+      <c r="K48" s="1" t="inlineStr"/>
+      <c r="L48" s="1" t="inlineStr"/>
+      <c r="M48" s="1" t="inlineStr"/>
+      <c r="N48" s="1" t="inlineStr">
+        <is>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>L189: isolated marker/symbol line :: .7</t>
+        </is>
+      </c>
+      <c r="P48" s="1" t="inlineStr"/>
+      <c r="Q48" s="1" t="inlineStr"/>
+      <c r="R48" s="1" t="inlineStr"/>
+      <c r="S48" s="1" t="inlineStr"/>
+      <c r="T48" s="1" t="inlineStr"/>
+      <c r="U48" s="1" t="inlineStr"/>
+      <c r="V48" s="1" t="inlineStr"/>
+      <c r="W48" s="1" t="inlineStr"/>
+      <c r="X48" s="1" t="inlineStr"/>
+      <c r="Y48" s="1" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr"/>
+      <c r="B49" s="1" t="inlineStr"/>
+      <c r="C49" s="1" t="inlineStr"/>
+      <c r="D49" s="1" t="inlineStr"/>
+      <c r="E49" s="1" t="inlineStr"/>
+      <c r="F49" s="1" t="inlineStr"/>
+      <c r="G49" s="1" t="inlineStr"/>
+      <c r="H49" s="1" t="inlineStr"/>
+      <c r="I49" s="1" t="inlineStr"/>
+      <c r="J49" s="1" t="inlineStr"/>
+      <c r="K49" s="1" t="inlineStr"/>
+      <c r="L49" s="1" t="inlineStr"/>
+      <c r="M49" s="1" t="inlineStr"/>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>L92: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr"/>
+      <c r="P49" s="1" t="inlineStr"/>
+      <c r="Q49" s="1" t="inlineStr"/>
+      <c r="R49" s="1" t="inlineStr"/>
+      <c r="S49" s="1" t="inlineStr"/>
+      <c r="T49" s="1" t="inlineStr"/>
+      <c r="U49" s="1" t="inlineStr"/>
+      <c r="V49" s="1" t="inlineStr"/>
+      <c r="W49" s="1" t="inlineStr"/>
+      <c r="X49" s="1" t="inlineStr"/>
+      <c r="Y49" s="1" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr"/>
+      <c r="B50" s="1" t="inlineStr"/>
+      <c r="C50" s="1" t="inlineStr"/>
+      <c r="D50" s="1" t="inlineStr"/>
+      <c r="E50" s="1" t="inlineStr"/>
+      <c r="F50" s="1" t="inlineStr"/>
+      <c r="G50" s="1" t="inlineStr"/>
+      <c r="H50" s="1" t="inlineStr"/>
+      <c r="I50" s="1" t="inlineStr"/>
+      <c r="J50" s="1" t="inlineStr"/>
+      <c r="K50" s="1" t="inlineStr"/>
+      <c r="L50" s="1" t="inlineStr"/>
+      <c r="M50" s="1" t="inlineStr"/>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t>L95: isolated marker/symbol line :: 58</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr"/>
+      <c r="P50" s="1" t="inlineStr"/>
+      <c r="Q50" s="1" t="inlineStr"/>
+      <c r="R50" s="1" t="inlineStr"/>
+      <c r="S50" s="1" t="inlineStr"/>
+      <c r="T50" s="1" t="inlineStr"/>
+      <c r="U50" s="1" t="inlineStr"/>
+      <c r="V50" s="1" t="inlineStr"/>
+      <c r="W50" s="1" t="inlineStr"/>
+      <c r="X50" s="1" t="inlineStr"/>
+      <c r="Y50" s="1" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr"/>
+      <c r="B51" s="1" t="inlineStr"/>
+      <c r="C51" s="1" t="inlineStr"/>
+      <c r="D51" s="1" t="inlineStr"/>
+      <c r="E51" s="1" t="inlineStr"/>
+      <c r="F51" s="1" t="inlineStr"/>
+      <c r="G51" s="1" t="inlineStr"/>
+      <c r="H51" s="1" t="inlineStr"/>
+      <c r="I51" s="1" t="inlineStr"/>
+      <c r="J51" s="1" t="inlineStr"/>
+      <c r="K51" s="1" t="inlineStr"/>
+      <c r="L51" s="1" t="inlineStr"/>
+      <c r="M51" s="1" t="inlineStr"/>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>L97: symbol-only separator/garbage line :: 58-59</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr"/>
+      <c r="P51" s="1" t="inlineStr"/>
+      <c r="Q51" s="1" t="inlineStr"/>
+      <c r="R51" s="1" t="inlineStr"/>
+      <c r="S51" s="1" t="inlineStr"/>
+      <c r="T51" s="1" t="inlineStr"/>
+      <c r="U51" s="1" t="inlineStr"/>
+      <c r="V51" s="1" t="inlineStr"/>
+      <c r="W51" s="1" t="inlineStr"/>
+      <c r="X51" s="1" t="inlineStr"/>
+      <c r="Y51" s="1" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" s="1" t="inlineStr"/>
+      <c r="C52" s="1" t="inlineStr"/>
+      <c r="D52" s="1" t="inlineStr"/>
+      <c r="E52" s="1" t="inlineStr"/>
+      <c r="F52" s="1" t="inlineStr"/>
+      <c r="G52" s="1" t="inlineStr"/>
+      <c r="H52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr"/>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
+      <c r="L52" s="1" t="inlineStr"/>
+      <c r="M52" s="1" t="inlineStr"/>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>L99: isolated marker/symbol line :: 57</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr"/>
+      <c r="P52" s="1" t="inlineStr"/>
+      <c r="Q52" s="1" t="inlineStr"/>
+      <c r="R52" s="1" t="inlineStr"/>
+      <c r="S52" s="1" t="inlineStr"/>
+      <c r="T52" s="1" t="inlineStr"/>
+      <c r="U52" s="1" t="inlineStr"/>
+      <c r="V52" s="1" t="inlineStr"/>
+      <c r="W52" s="1" t="inlineStr"/>
+      <c r="X52" s="1" t="inlineStr"/>
+      <c r="Y52" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
